--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -175,15 +175,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標7)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標7)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -201,14 +212,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$4:$Q$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>2</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -228,9 +317,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -238,14 +341,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -266,15 +371,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標12)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標12)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -292,14 +408,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$13:$Q$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -319,9 +513,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -332,11 +540,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -357,15 +567,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標5)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標5)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -383,14 +604,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$4:$O$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -410,9 +667,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -423,11 +694,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -448,15 +721,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -474,14 +758,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$5:$O$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -501,9 +821,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -514,11 +848,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -539,15 +875,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -565,14 +912,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$6:$O$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -592,9 +975,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -605,11 +1002,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -630,15 +1029,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -656,14 +1066,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$7:$O$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -683,9 +1129,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -696,11 +1156,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -721,15 +1183,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標18)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標18)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -747,14 +1220,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$8:$O$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -774,9 +1283,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -787,11 +1310,13 @@
           <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -812,15 +1337,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標38)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標38)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -838,14 +1374,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$9:$O$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -865,9 +1437,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -875,14 +1461,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -903,15 +1491,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -929,14 +1528,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$10:$O$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -956,9 +1591,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -969,11 +1618,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -994,15 +1645,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標19)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標19)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1020,14 +1682,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$11:$O$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>4</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>2</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1047,9 +1745,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1060,11 +1772,13 @@
           <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1085,15 +1799,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1111,14 +1836,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$12:$O$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1138,9 +1899,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1151,11 +1926,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1176,15 +1953,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標12)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標12)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1202,14 +1990,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$5:$Q$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>2</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1229,9 +2095,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1242,11 +2122,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1267,15 +2149,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標9)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標9)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1293,14 +2186,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'亀本'!$I$3:$O$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>大島　貞男</v>
+              </pt>
+              <pt idx="1">
+                <v>杉澤　修平</v>
+              </pt>
+              <pt idx="2">
+                <v>平館　健</v>
+              </pt>
+              <pt idx="3">
+                <v>平賀　崇</v>
+              </pt>
+              <pt idx="4">
+                <v>安部　雅史</v>
+              </pt>
+              <pt idx="5">
+                <v>田中　智久</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'亀本'!$I$13:$O$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1320,9 +2249,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1333,11 +2276,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1358,15 +2303,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標5)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標5)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1384,14 +2340,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$4:$N$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>3</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>3</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1411,9 +2403,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1424,11 +2430,13 @@
           <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1449,15 +2457,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1475,14 +2494,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$5:$N$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>2</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>3</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1502,9 +2557,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1515,11 +2584,13 @@
           <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1540,15 +2611,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1566,14 +2648,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$6:$N$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1593,9 +2711,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1606,11 +2738,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1631,15 +2765,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1657,14 +2802,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$7:$N$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>2</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>3</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1684,9 +2865,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1697,11 +2892,13 @@
           <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1722,15 +2919,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標19)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標19)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1748,14 +2956,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$8:$N$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>2</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1775,9 +3019,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1788,11 +3046,13 @@
           <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1813,15 +3073,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標31)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標31)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1839,14 +3110,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$9:$N$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>3</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+              <pt idx="4">
+                <v>3</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1866,9 +3173,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1876,14 +3197,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1904,15 +3227,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1930,14 +3264,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$10:$N$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -1957,9 +3327,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1970,11 +3354,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -1995,15 +3381,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標16)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標16)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2021,14 +3418,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$11:$N$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2048,9 +3481,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2058,14 +3505,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2086,15 +3535,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2112,14 +3572,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$12:$N$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2139,9 +3635,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2152,11 +3662,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2177,15 +3689,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標12)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標12)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2203,14 +3726,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$6:$Q$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2230,9 +3831,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2243,11 +3858,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2268,15 +3885,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2294,14 +3922,50 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'神山'!$I$3:$N$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>水嶋　規雄</v>
+              </pt>
+              <pt idx="1">
+                <v>竹村　優希</v>
+              </pt>
+              <pt idx="2">
+                <v>竹内　杏</v>
+              </pt>
+              <pt idx="3">
+                <v>芳賀　芳勝</v>
+              </pt>
+              <pt idx="4">
+                <v>中原　義美</v>
+              </pt>
+              <pt idx="5">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'神山'!$I$13:$N$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="6"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2321,9 +3985,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2334,11 +4012,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2359,15 +4039,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2385,14 +4076,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$4:$L$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2412,9 +4127,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2425,11 +4154,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2450,15 +4181,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2476,14 +4218,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$5:$L$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2503,9 +4269,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2513,14 +4293,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2541,15 +4323,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2567,14 +4360,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$6:$L$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2594,9 +4411,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2604,14 +4435,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2632,15 +4465,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2658,14 +4502,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$7:$L$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>3</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2685,9 +4553,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2695,14 +4577,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2723,15 +4607,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標6)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標6)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2749,14 +4644,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$8:$L$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2776,9 +4695,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2789,11 +4722,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2814,15 +4749,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標14)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標14)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2840,14 +4786,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$9:$L$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>2</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2867,9 +4837,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2877,14 +4861,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2905,15 +4891,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2931,14 +4928,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$10:$L$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -2958,9 +4979,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2971,11 +5006,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -2996,15 +5033,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標6)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標6)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3022,14 +5070,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$11:$L$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>3</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3049,9 +5121,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3062,11 +5148,13 @@
           <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3087,15 +5175,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3113,14 +5212,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$12:$L$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3140,9 +5263,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3150,14 +5287,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3178,15 +5317,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標12)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標12)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3204,14 +5354,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$7:$Q$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>2</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>1</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3231,9 +5459,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3244,11 +5486,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3269,15 +5513,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3295,14 +5550,38 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'森'!$I$3:$L$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>山本　雅巳</v>
+              </pt>
+              <pt idx="1">
+                <v>佐々木　達哉</v>
+              </pt>
+              <pt idx="2">
+                <v>樫原　純二</v>
+              </pt>
+              <pt idx="3">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'森'!$I$13:$L$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="4"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3322,9 +5601,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3332,14 +5625,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3360,15 +5655,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標2)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標2)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3386,14 +5692,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$4:$K$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3413,9 +5731,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3426,11 +5758,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3451,15 +5785,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3477,14 +5822,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$5:$K$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3504,9 +5861,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3517,11 +5888,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3542,15 +5915,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3568,14 +5952,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$6:$K$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3595,9 +5991,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3608,11 +6018,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3633,15 +6045,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3659,14 +6082,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$7:$K$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>5</v>
+              </pt>
+              <pt idx="1">
+                <v>2</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3686,9 +6121,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3696,14 +6145,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3724,15 +6175,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標8)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標8)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3750,14 +6212,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$8:$K$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3777,9 +6251,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3787,14 +6275,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3815,15 +6305,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標15)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標15)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3841,14 +6342,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$9:$K$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>3</v>
+              </pt>
+              <pt idx="1">
+                <v>2</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3868,9 +6381,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3878,14 +6405,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3906,15 +6435,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -3932,14 +6472,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$10:$K$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>2</v>
+              </pt>
+              <pt idx="1">
+                <v>4</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -3959,9 +6511,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -3969,14 +6535,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -3997,15 +6565,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標5)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標5)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4023,14 +6602,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$11:$K$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>7</v>
+              </pt>
+              <pt idx="1">
+                <v>7</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4050,9 +6641,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4060,14 +6665,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4088,15 +6695,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4114,14 +6732,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$12:$K$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4141,9 +6771,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4154,11 +6798,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4179,15 +6825,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標25)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標25)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4205,14 +6862,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$8:$Q$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>5</v>
+              </pt>
+              <pt idx="3">
+                <v>3</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>1</v>
+              </pt>
+              <pt idx="9">
+                <v>1</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4232,9 +6967,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4242,14 +6991,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4270,15 +7021,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標4)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標4)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4296,14 +7058,26 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'北檜山'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>大森　英樹</v>
+              </pt>
+              <pt idx="1">
+                <v>赤平　恵一</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'北檜山'!$I$13:$K$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="2"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4323,9 +7097,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4336,11 +7124,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4361,15 +7151,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エンジンリフレッシュ(目標2)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エンジンリフレッシュ</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標2)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4387,14 +7188,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$4:$K$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4414,9 +7233,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4427,11 +7260,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4452,15 +7287,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン潤滑剤 NC200マキシクール(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4478,14 +7324,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$5:$K$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4505,9 +7369,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4515,14 +7393,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4543,15 +7423,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ウィンドウ撥水12カ月(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ウィンドウ撥水12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4569,14 +7460,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$6:$K$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4596,9 +7505,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4606,14 +7529,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4634,15 +7559,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>エアコン/ヒーター洗浄12カ月(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>エアコン/ヒーター洗浄12カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4660,14 +7596,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$7:$K$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4687,9 +7641,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4697,14 +7665,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4725,15 +7695,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>メタルトリートメント MT-10(目標7)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>メタルトリートメント MT-10</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標7)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4751,14 +7732,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$8:$K$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4778,9 +7777,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4788,14 +7801,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4816,15 +7831,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標13)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標13)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4842,14 +7868,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$9:$K$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4869,9 +7913,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4879,14 +7937,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4907,15 +7967,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -4933,14 +8004,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$10:$K$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -4960,9 +8049,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -4970,14 +8073,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -4998,15 +8103,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標5)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標5)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5024,14 +8140,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$11:$K$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5051,9 +8185,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5061,14 +8209,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5089,15 +8239,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5115,14 +8276,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$12:$K$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5142,9 +8321,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5152,14 +8345,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5180,15 +8375,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>クーラントエナジー(目標59)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>クーラントエナジー</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標59)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5206,14 +8412,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$9:$Q$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>4</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+              <pt idx="5">
+                <v>1</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5233,9 +8517,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5243,14 +8541,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5271,15 +8571,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ギヤボックス添加剤　SuperADD1201(目標3)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標3)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5297,14 +8608,32 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'江差'!$I$3:$K$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>高根　拓也</v>
+              </pt>
+              <pt idx="1">
+                <v>今泉　健一</v>
+              </pt>
+              <pt idx="2">
+                <v>(担当CA不明)</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'江差'!$I$13:$K$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="3"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5324,9 +8653,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5334,14 +8677,16 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5362,15 +8707,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>エンジンリフレッシュ</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5388,14 +8735,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$4:$M$4</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5415,9 +8792,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5428,11 +8819,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5453,15 +8846,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>エアコン潤滑剤 NC200マキシクール</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5479,14 +8874,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$5:$M$5</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5506,9 +8931,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5519,11 +8958,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5544,15 +8985,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>ウィンドウ撥水12カ月</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5570,14 +9013,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$6:$M$6</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5597,9 +9070,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5610,11 +9097,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5635,15 +9124,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>エアコン/ヒーター洗浄12カ月</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5661,14 +9152,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$7:$M$7</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5688,9 +9209,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5701,11 +9236,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5726,15 +9263,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>メタルトリートメント MT-10</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5752,14 +9291,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$8:$M$8</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5779,9 +9348,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5792,11 +9375,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5817,15 +9402,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>クーラントエナジー</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5843,14 +9430,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$9:$M$9</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5870,9 +9487,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5883,11 +9514,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5908,15 +9541,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>抗菌・抗ウィルスコート</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -5934,14 +9569,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$10:$M$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -5961,9 +9626,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -5974,11 +9653,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -5999,15 +9680,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>ボディーコート3カ月</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6025,14 +9708,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$11:$M$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>1</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6052,9 +9765,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6065,11 +9792,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6090,15 +9819,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6116,14 +9847,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$12:$M$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6143,9 +9904,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6156,11 +9931,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6181,15 +9958,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>抗菌・抗ウィルスコート(目標15)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>抗菌・抗ウィルスコート</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標15)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6207,14 +9995,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$10:$Q$10</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>2</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6234,9 +10100,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6247,11 +10127,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6272,15 +10154,17 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
               <a:t>ギヤボックス添加剤　SuperADD1201</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6298,14 +10182,44 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$3:$M$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="1">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="2">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="3">
+                <v>秋山　泰賢</v>
+              </pt>
+              <pt idx="4">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'クエスト5・U-Car石川'!$I$13:$M$13</f>
-            </numRef>
+            <numLit>
+              <ptCount val="5"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6325,9 +10239,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6338,11 +10266,13 @@
           <max val="1"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6363,15 +10293,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ボディーコート3カ月(目標30)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>ボディーコート3カ月</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標30)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6389,14 +10330,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$11:$Q$11</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>1</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>3</v>
+              </pt>
+              <pt idx="3">
+                <v>2</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>1</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>1</v>
+              </pt>
+              <pt idx="11">
+                <v>1</v>
+              </pt>
+              <pt idx="12">
+                <v>1</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6416,9 +10435,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6429,11 +10462,13 @@
           <max val="4"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6454,15 +10489,26 @@
         <rich>
           <a:bodyPr/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>NISMOオイル / Mobil1オイル （台数）(目標12)</a:t>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>NISMOオイル / Mobil1オイル （台数）</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1400" b="1"/>
+              <a:t>(目標12)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -6480,14 +10526,92 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
-              <f>'石川'!$I$3:$Q$3</f>
-            </numRef>
+            <strLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>加藤　英基</v>
+              </pt>
+              <pt idx="1">
+                <v>川村　正敏</v>
+              </pt>
+              <pt idx="2">
+                <v>村上　英俊</v>
+              </pt>
+              <pt idx="3">
+                <v>阿部　隆二</v>
+              </pt>
+              <pt idx="4">
+                <v>野呂　藍亮</v>
+              </pt>
+              <pt idx="5">
+                <v>小野　翼</v>
+              </pt>
+              <pt idx="6">
+                <v>橋本　隆志</v>
+              </pt>
+              <pt idx="7">
+                <v>岩坪　公夫</v>
+              </pt>
+              <pt idx="8">
+                <v>落合　典彦</v>
+              </pt>
+              <pt idx="9">
+                <v>鈴木　聡</v>
+              </pt>
+              <pt idx="10">
+                <v>(担当CA不明)</v>
+              </pt>
+              <pt idx="11">
+                <v>前野　正樹</v>
+              </pt>
+              <pt idx="12">
+                <v>石澤　直道</v>
+              </pt>
+            </strLit>
           </cat>
           <val>
-            <numRef>
-              <f>'石川'!$I$12:$Q$12</f>
-            </numRef>
+            <numLit>
+              <ptCount val="13"/>
+              <pt idx="0">
+                <v>0</v>
+              </pt>
+              <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
+                <v>1</v>
+              </pt>
+              <pt idx="3">
+                <v>0</v>
+              </pt>
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
+              </pt>
+              <pt idx="7">
+                <v>0</v>
+              </pt>
+              <pt idx="8">
+                <v>0</v>
+              </pt>
+              <pt idx="9">
+                <v>0</v>
+              </pt>
+              <pt idx="10">
+                <v>0</v>
+              </pt>
+              <pt idx="11">
+                <v>0</v>
+              </pt>
+              <pt idx="12">
+                <v>0</v>
+              </pt>
+            </numLit>
           </val>
         </ser>
         <dLbls>
@@ -6507,9 +10631,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr vert="eaVert"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -6520,11 +10658,13 @@
           <max val="2"/>
           <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
         <crossAx val="10"/>
         <majorUnit val="1"/>
         <minorUnit val="1"/>
@@ -6652,7 +10792,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6674,7 +10814,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6696,7 +10836,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6718,7 +10858,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6740,7 +10880,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6877,7 +11017,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6899,7 +11039,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6921,7 +11061,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6943,7 +11083,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -6965,7 +11105,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7102,7 +11242,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7124,7 +11264,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7146,7 +11286,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7168,7 +11308,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7190,7 +11330,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7327,7 +11467,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7349,7 +11489,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7371,7 +11511,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7393,7 +11533,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7415,7 +11555,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7552,7 +11692,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7574,7 +11714,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7596,7 +11736,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7618,7 +11758,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7640,7 +11780,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7777,7 +11917,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7799,7 +11939,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7821,7 +11961,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7843,7 +11983,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -7865,7 +12005,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8002,7 +12142,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8024,7 +12164,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8046,7 +12186,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8068,7 +12208,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8090,7 +12230,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="5040000"/>
@@ -8400,7 +12540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -8418,6 +12558,10 @@
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8499,13 +12643,49 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>そ
-の
-他</t>
+          <t>落
+合
+典
+彦</t>
         </is>
       </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>鈴
+木
+聡</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>(
+担
+当
+C
+A
+不
+明
+)</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>前
+野
+正
+樹</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>石
+澤
+直
+道</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -8518,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -8538,8 +12718,20 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -8552,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
@@ -8570,6 +12762,18 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8586,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>0</v>
@@ -8604,6 +12808,18 @@
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8617,10 +12833,10 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>0</v>
@@ -8639,6 +12855,18 @@
       </c>
       <c r="Q7" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8648,16 +12876,16 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -8672,7 +12900,19 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8688,7 +12928,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -8706,6 +12946,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8722,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
@@ -8740,6 +12992,18 @@
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8750,16 +13014,16 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -8774,7 +13038,19 @@
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -8790,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="4" t="n">
         <v>0</v>
@@ -8808,6 +13084,18 @@
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8842,6 +13130,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8858,7 +13158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -8873,7 +13173,6 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -8936,15 +13235,8 @@
 久</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>そ
-の
-他</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -8968,11 +13260,8 @@
       <c r="N4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -8994,9 +13283,6 @@
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9022,10 +13308,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -9047,12 +13330,9 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9072,15 +13352,12 @@
         <v>0</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9100,16 +13377,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -9136,9 +13410,6 @@
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -9164,9 +13435,6 @@
       <c r="N11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
@@ -9192,9 +13460,6 @@
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -9218,9 +13483,6 @@
         <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9309,13 +13571,18 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>そ
-の
-他</t>
+          <t>(
+担
+当
+C
+A
+不
+明
+)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -9340,7 +13607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -9456,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>3</v>
@@ -9634,20 +13901,25 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>そ
-の
-他</t>
+          <t>(
+担
+当
+C
+A
+不
+明
+)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
@@ -9659,7 +13931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -9669,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
@@ -9704,7 +13976,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
@@ -9742,10 +14014,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0</v>
@@ -9843,7 +14115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -9854,7 +14126,6 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -9887,15 +14158,8 @@
 一</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>そ
-の
-他</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -9907,11 +14171,8 @@
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -9921,9 +14182,6 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9939,9 +14197,6 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="H7" s="4" t="inlineStr">
@@ -9950,13 +14205,10 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9971,9 +14223,6 @@
       <c r="J8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="H9" s="4" t="inlineStr">
@@ -9982,13 +14231,10 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10001,10 +14247,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -10014,13 +14257,10 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -10035,9 +14275,6 @@
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -10049,9 +14286,6 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10114,13 +14348,18 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>そ
-の
-他</t>
+          <t>(
+担
+当
+C
+A
+不
+明
+)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -10136,7 +14375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -10363,7 +14602,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="396.8503937007874" customHeight="1">
+    <row r="4" ht="51.02362204724409" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -10385,7 +14624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="396.8503937007874" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -10536,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
